--- a/ru/downloads/data-excel/3.3.1.xlsx
+++ b/ru/downloads/data-excel/3.3.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F70945-40CC-4CCA-B1A9-93F0695C706C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14535" yWindow="435" windowWidth="13050" windowHeight="12990"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="61">
   <si>
     <t>Кыргызская Республика</t>
   </si>
@@ -179,12 +180,30 @@
   </si>
   <si>
     <t>3.3.1 Число новых заражений ВИЧ на 1000 неинфицированных в разбивке по полу, возрасту и территории</t>
+  </si>
+  <si>
+    <t>15-28</t>
+  </si>
+  <si>
+    <t>29 and  over</t>
+  </si>
+  <si>
+    <t>15-28 жаш</t>
+  </si>
+  <si>
+    <t>15-28 лет</t>
+  </si>
+  <si>
+    <t>29  жаш жана андан улуу</t>
+  </si>
+  <si>
+    <t>29 и старше</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -357,12 +376,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -371,19 +387,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -395,52 +405,38 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -452,29 +448,26 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="2"/>
-    <cellStyle name="Обычный 4" xfId="1"/>
-    <cellStyle name="Обычный 5" xfId="5"/>
-    <cellStyle name="Обычный 6" xfId="3"/>
-    <cellStyle name="Обычный 7" xfId="6"/>
-    <cellStyle name="Обычный_ССП Социальный" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 5" xfId="5" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 6" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 7" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный_ССП Социальный" xfId="4" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -490,9 +483,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -530,9 +523,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -567,7 +560,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -602,7 +595,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -775,11 +768,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.140625" customWidth="1"/>
@@ -798,2168 +791,2395 @@
     <col min="15" max="15" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="8" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:21" s="6" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-    </row>
-    <row r="2" spans="1:20" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+    </row>
+    <row r="2" spans="1:21" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
+      <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="9">
         <v>2007</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="9">
         <v>2008</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="9">
         <v>2009</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="9">
         <v>2010</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="9">
         <v>2011</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="9">
         <v>2012</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="9">
         <v>2013</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="9">
         <v>2014</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="9">
         <v>2015</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="9">
         <v>2016</v>
       </c>
-      <c r="N3" s="12">
+      <c r="N3" s="9">
         <v>2017</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="9">
         <v>2018</v>
       </c>
-      <c r="P3" s="12">
+      <c r="P3" s="9">
         <v>2019</v>
       </c>
-      <c r="Q3" s="12">
+      <c r="Q3" s="9">
         <v>2020</v>
       </c>
-      <c r="R3" s="12">
+      <c r="R3" s="9">
         <v>2021</v>
       </c>
-      <c r="S3" s="12">
+      <c r="S3" s="9">
         <v>2022</v>
       </c>
-      <c r="T3" s="12">
+      <c r="T3" s="9">
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="U3" s="9">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="17" t="s">
+      <c r="B4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="17">
         <v>7.7638926221379898E-2</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="17">
         <v>0.10379496583133657</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="17">
         <v>0.12466080556518534</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="17">
         <v>0.101699781510686</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="17">
         <v>0.10772266310734545</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="17">
         <v>0.12556166103095753</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="15">
         <v>8.3925298092168157E-2</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="15">
         <v>0.10488065198748836</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="15">
         <v>0.10156688321957283</v>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="15">
         <v>0.11745109412109569</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="15">
         <v>0.12843538433562685</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="15">
         <v>0.12969973719986175</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="25">
         <v>0.1</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="25">
         <v>0.1</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="25">
         <v>0.12641839647678207</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="25">
         <v>0.15686557910355481</v>
       </c>
-      <c r="T4" s="35">
+      <c r="T4" s="25">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="U4" s="25">
+        <v>0.14582841410560995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="16">
         <v>4.1956223924862403E-2</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="16">
         <v>6.7162082885431504E-2</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="16">
         <v>6.455301985262106E-2</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="16">
         <v>6.0538787962713905E-2</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="16">
         <v>6.4473146934301867E-2</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="16">
         <v>0.10574766773518809</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="11">
         <v>7.0194195873618637E-2</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="11">
         <v>9.0884735772978079E-2</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="11">
         <v>9.108845719756721E-2</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="11">
         <v>9.7136747679148844E-2</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="11">
         <v>0.10652700219579983</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="11">
         <v>9.7581515864526736E-2</v>
       </c>
-      <c r="P5" s="34">
+      <c r="P5" s="11">
         <v>0.1</v>
       </c>
-      <c r="Q5" s="34">
+      <c r="Q5" s="11">
         <v>0.1</v>
       </c>
-      <c r="R5" s="34">
+      <c r="R5" s="11">
         <v>0.14922981985616976</v>
       </c>
-      <c r="S5" s="34">
+      <c r="S5" s="11">
         <v>0.18747863920572591</v>
       </c>
-      <c r="T5" s="34">
+      <c r="T5" s="11">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="U5" s="11">
+        <v>0.17789463210485534</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="19">
         <v>0.11429552203998651</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="19">
         <v>0.14143009845974616</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="19">
         <v>0.18635890466141974</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="19">
         <v>0.1439280226000467</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="19">
         <v>0.15207728758770156</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="19">
         <v>0.14585548393152736</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="19">
         <v>9.7970039559382396E-2</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="19">
         <v>0.11917902282901899</v>
       </c>
-      <c r="L6" s="24">
+      <c r="L6" s="19">
         <v>0.11225662610844939</v>
       </c>
-      <c r="M6" s="24">
+      <c r="M6" s="19">
         <v>0.13814695781138026</v>
       </c>
-      <c r="N6" s="24">
+      <c r="N6" s="19">
         <v>0.15073081657361834</v>
       </c>
-      <c r="O6" s="24">
+      <c r="O6" s="19">
         <v>0.16234926078458389</v>
       </c>
-      <c r="P6" s="36">
+      <c r="P6" s="26">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="36">
+      <c r="Q6" s="26">
         <v>0.1</v>
       </c>
-      <c r="R6" s="36">
+      <c r="R6" s="26">
         <v>0.10326895933792253</v>
       </c>
-      <c r="S6" s="36">
+      <c r="S6" s="26">
         <v>0.12556588018347117</v>
       </c>
-      <c r="T6" s="36">
+      <c r="T6" s="26">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="U6" s="26">
+        <v>0.11308328864117552</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="17">
         <v>1.8993803271682614E-2</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="17">
         <v>3.7672587541675302E-2</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="17">
         <v>1.6262429142273022E-2</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="17">
         <v>1.1429956086108717E-2</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="17">
         <v>2.4721101032892549E-2</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="17">
         <v>3.9660506068057433E-2</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="15">
         <v>3.8771378107095161E-2</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="15">
         <v>7.1557555425535949E-2</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="15">
         <v>5.1375211665872063E-2</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="15">
         <v>3.4134010123745825E-2</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="15">
         <v>5.1128062030138026E-2</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="15">
         <v>4.0436093642290762E-2</v>
       </c>
-      <c r="P7" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="38">
-        <v>0</v>
-      </c>
-      <c r="R7" s="38">
+      <c r="P7" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="25">
+        <v>0</v>
+      </c>
+      <c r="R7" s="25">
         <v>3.433011112114915E-2</v>
       </c>
-      <c r="S7" s="38">
+      <c r="S7" s="25">
         <v>5.1313356512815066E-2</v>
       </c>
-      <c r="T7" s="38">
+      <c r="T7" s="25">
         <v>5.1313356512815066E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="U7" s="25">
+        <v>5.9422548650089474E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="16">
         <v>1.4483447833034815E-2</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="16">
         <v>3.3537432565805228E-2</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="16">
         <v>4.7286466140525922E-3</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="16">
         <v>1.3943306515707136E-2</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="16">
         <v>2.2820525693629877E-2</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="16">
         <v>4.0276385507661466E-2</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="11">
         <v>4.3778620273003478E-2</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="11">
         <v>7.7045559607581277E-2</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="11">
         <v>6.2727386777066879E-2</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="11">
         <v>3.2702849644560904E-2</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="11">
         <v>4.4050570054422478E-2</v>
       </c>
-      <c r="O8" s="15">
+      <c r="O8" s="11">
         <v>3.5312119904264916E-2</v>
       </c>
-      <c r="P8" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="36">
-        <v>0</v>
-      </c>
-      <c r="R8" s="36">
+      <c r="P8" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="26">
+        <v>0</v>
+      </c>
+      <c r="R8" s="26">
         <v>3.6820478077087354E-2</v>
       </c>
-      <c r="S8" s="36">
+      <c r="S8" s="26">
         <v>6.0745743331368028E-2</v>
       </c>
-      <c r="T8" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="T8" s="26">
+        <v>0</v>
+      </c>
+      <c r="U8" s="26">
+        <v>7.9000879314134964E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="19">
         <v>2.3358264387522948E-2</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="19">
         <v>4.166859576832261E-2</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="19">
         <v>2.7401889817001045E-2</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="19">
         <v>8.9972558369697253E-3</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="19">
         <v>2.6564775992526442E-2</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="19">
         <v>3.9063178180176739E-2</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="19">
         <v>3.3921590244150646E-2</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="19">
         <v>6.624874748461787E-2</v>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="19">
         <v>4.040632601440082E-2</v>
       </c>
-      <c r="M9" s="24">
+      <c r="M9" s="19">
         <v>3.551556765715639E-2</v>
       </c>
-      <c r="N9" s="24">
+      <c r="N9" s="19">
         <v>5.7956679314102019E-2</v>
       </c>
-      <c r="O9" s="24">
+      <c r="O9" s="19">
         <v>4.5374109533100414E-2</v>
       </c>
-      <c r="P9" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="36">
-        <v>0</v>
-      </c>
-      <c r="R9" s="36">
+      <c r="P9" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="26">
+        <v>0</v>
+      </c>
+      <c r="R9" s="26">
         <v>3.1930519190242035E-2</v>
       </c>
-      <c r="S9" s="36">
+      <c r="S9" s="26">
         <v>4.2060988433228183E-2</v>
       </c>
-      <c r="T9" s="36">
+      <c r="T9" s="26">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="U9" s="26">
+        <v>4.0286571814171473E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="17">
         <v>4.45353144800502E-2</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="17">
         <v>7.0042095299274867E-2</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="17">
         <v>6.0105036013755185E-2</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="17">
         <v>5.9233249856529301E-2</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="17">
         <v>4.8785900683385244E-2</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="17">
         <v>9.1048778679191977E-2</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="15">
         <v>4.6879610402861309E-2</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="15">
         <v>7.2025677153905371E-2</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="15">
         <v>8.2865744271023875E-2</v>
       </c>
-      <c r="M10" s="19">
+      <c r="M10" s="15">
         <v>6.3928013601116843E-2</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="15">
         <v>0.10258288442723991</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="15">
         <v>6.1541941664892491E-2</v>
       </c>
-      <c r="P10" s="38">
+      <c r="P10" s="25">
         <v>0.1</v>
       </c>
-      <c r="Q10" s="38">
-        <v>0</v>
-      </c>
-      <c r="R10" s="38">
+      <c r="Q10" s="25">
+        <v>0</v>
+      </c>
+      <c r="R10" s="25">
         <v>8.7302929367211068E-2</v>
       </c>
-      <c r="S10" s="38">
+      <c r="S10" s="25">
         <v>9.2022006630303563E-2</v>
       </c>
-      <c r="T10" s="38">
+      <c r="T10" s="25">
         <v>9.2808519507485643E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="U10" s="25">
+        <v>8.3143044638906788E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="16">
         <v>3.8468313245450109E-2</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="16">
         <v>5.6059535226410447E-2</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="16">
         <v>4.7336344450799789E-2</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="16">
         <v>5.8324114882953221E-2</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="16">
         <v>3.6397212356662031E-2</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="16">
         <v>9.5921096434556416E-2</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="11">
         <v>5.160148907154178E-2</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="11">
         <v>6.5024320902248578E-2</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="11">
         <v>8.1427602895282322E-2</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="11">
         <v>4.3400668023082206E-2</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="11">
         <v>0.10741083621893398</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="11">
         <v>6.1918053965767689E-2</v>
       </c>
-      <c r="P11" s="36">
+      <c r="P11" s="26">
         <v>0.1</v>
       </c>
-      <c r="Q11" s="36">
-        <v>0</v>
-      </c>
-      <c r="R11" s="36">
+      <c r="Q11" s="26">
+        <v>0</v>
+      </c>
+      <c r="R11" s="26">
         <v>0.10296328329317765</v>
       </c>
-      <c r="S11" s="36">
+      <c r="S11" s="26">
         <v>7.8942235953699605E-2</v>
       </c>
-      <c r="T11" s="36">
+      <c r="T11" s="26">
         <v>0.10511425919975013</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="U11" s="26">
+        <v>9.4210256356575359E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="19">
         <v>5.0600424638763568E-2</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="19">
         <v>8.4011761646630517E-2</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="19">
         <v>7.2851854768843038E-2</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="19">
         <v>6.0140457067473709E-2</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="19">
         <v>6.1142680265817803E-2</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="19">
         <v>8.6194619956677834E-2</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="19">
         <v>4.2180705811584285E-2</v>
       </c>
-      <c r="K12" s="24">
+      <c r="K12" s="19">
         <v>7.8983837034803148E-2</v>
       </c>
-      <c r="L12" s="24">
+      <c r="L12" s="19">
         <v>8.4292452664519554E-2</v>
       </c>
-      <c r="M12" s="24">
+      <c r="M12" s="19">
         <v>8.4261354647443609E-2</v>
       </c>
-      <c r="N12" s="24">
+      <c r="N12" s="19">
         <v>9.7807592230029966E-2</v>
       </c>
-      <c r="O12" s="24">
+      <c r="O12" s="19">
         <v>6.1170371056164324E-2</v>
       </c>
-      <c r="P12" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="36">
-        <v>0</v>
-      </c>
-      <c r="R12" s="36">
+      <c r="P12" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="26">
+        <v>0</v>
+      </c>
+      <c r="R12" s="26">
         <v>7.1859056271889668E-2</v>
       </c>
-      <c r="S12" s="36">
+      <c r="S12" s="26">
         <v>0.10098382728705417</v>
       </c>
-      <c r="T12" s="36">
+      <c r="T12" s="26">
         <v>7.3018905811696413E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="U12" s="26">
+        <v>7.2233139090068829E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="17">
         <v>4.6075199332831114E-3</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="17">
         <v>2.7500922426773065E-2</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="17">
         <v>2.7304934684320825E-2</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="17">
         <v>1.8062237956438399E-2</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="17">
         <v>5.37829588694822E-2</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="17">
         <v>3.1064169699121326E-2</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="15">
         <v>2.8512461042108517E-2</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="15">
         <v>6.2882171820113617E-2</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="15">
         <v>6.6387126893639264E-2</v>
       </c>
-      <c r="M13" s="19">
+      <c r="M13" s="15">
         <v>8.2385721498237155E-2</v>
       </c>
-      <c r="N13" s="19">
+      <c r="N13" s="15">
         <v>8.7531000562699288E-2</v>
       </c>
-      <c r="O13" s="19">
+      <c r="O13" s="15">
         <v>5.757218112208181E-2</v>
       </c>
-      <c r="P13" s="35">
+      <c r="P13" s="25">
         <v>0.1</v>
       </c>
-      <c r="Q13" s="35">
-        <v>0</v>
-      </c>
-      <c r="R13" s="35">
+      <c r="Q13" s="25">
+        <v>0</v>
+      </c>
+      <c r="R13" s="25">
         <v>0.10716050460690947</v>
       </c>
-      <c r="S13" s="35">
+      <c r="S13" s="25">
         <v>9.7010038673425045E-2</v>
       </c>
-      <c r="T13" s="35">
+      <c r="T13" s="25">
         <v>0.13486027182658078</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="U13" s="25">
+        <v>9.1402164037635764E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="20">
-        <v>0</v>
-      </c>
-      <c r="E14" s="20">
+      <c r="D14" s="16">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16">
         <v>2.2619828541699652E-2</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="16">
         <v>1.3496551631058265E-2</v>
       </c>
-      <c r="G14" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="20">
+      <c r="G14" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="16">
         <v>3.5536918416119549E-2</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="16">
         <v>2.6411240624009576E-2</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="11">
         <v>2.6122619576291112E-2</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="11">
         <v>6.4606995645488496E-2</v>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="11">
         <v>4.6816877910094569E-2</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="11">
         <v>7.1419568961895552E-2</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="11">
         <v>5.8072491060984416E-2</v>
       </c>
-      <c r="O14" s="15">
+      <c r="O14" s="11">
         <v>2.047242160086148E-2</v>
       </c>
-      <c r="P14" s="36">
+      <c r="P14" s="26">
         <v>0.1</v>
       </c>
-      <c r="Q14" s="36">
+      <c r="Q14" s="26">
         <v>0.1</v>
       </c>
-      <c r="R14" s="36">
+      <c r="R14" s="26">
         <v>7.9035451351703812E-2</v>
       </c>
-      <c r="S14" s="36">
+      <c r="S14" s="26">
         <v>0.12657756598786343</v>
       </c>
-      <c r="T14" s="36">
+      <c r="T14" s="26">
         <v>0.10706756701875898</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="U14" s="26">
+        <v>0.10609225636279161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="19">
         <v>9.3488961290895574E-3</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="19">
         <v>3.2512168840337384E-2</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="19">
         <v>4.1436082540676426E-2</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="19">
         <v>3.6491356110021432E-2</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="19">
         <v>7.2358900144717797E-2</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="19">
         <v>3.5793542844870789E-2</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="19">
         <v>3.0938542794634375E-2</v>
       </c>
-      <c r="K15" s="24">
+      <c r="K15" s="19">
         <v>6.1133502469356837E-2</v>
       </c>
-      <c r="L15" s="24">
+      <c r="L15" s="19">
         <v>8.620689655172413E-2</v>
       </c>
-      <c r="M15" s="24">
+      <c r="M15" s="19">
         <v>9.3476607478978388E-2</v>
       </c>
-      <c r="N15" s="24">
+      <c r="N15" s="19">
         <v>0.11727650449001474</v>
       </c>
-      <c r="O15" s="24">
+      <c r="O15" s="19">
         <v>9.4996179501476569E-2</v>
       </c>
-      <c r="P15" s="36">
+      <c r="P15" s="26">
         <v>0.1</v>
       </c>
-      <c r="Q15" s="36">
-        <v>0</v>
-      </c>
-      <c r="R15" s="36">
+      <c r="Q15" s="26">
+        <v>0</v>
+      </c>
+      <c r="R15" s="26">
         <v>0.13553052227085377</v>
       </c>
-      <c r="S15" s="36">
+      <c r="S15" s="26">
         <v>6.7310604785784003E-2</v>
       </c>
-      <c r="T15" s="36">
+      <c r="T15" s="26">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="U15" s="26">
+        <v>7.6730267532866131E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="21">
+      <c r="D16" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="17">
         <v>3.8892951041553233E-3</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="17">
         <v>7.7428446436936475E-3</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="17">
         <v>2.3010458253276113E-2</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="17">
         <v>9.487053966157781E-2</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="17">
         <v>4.5026284093339489E-2</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="15">
         <v>4.0785151238756277E-2</v>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="15">
         <v>8.7939146110891264E-2</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="15">
         <v>7.2443032610231134E-2</v>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="15">
         <v>8.950179719608771E-2</v>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="15">
         <v>0.12392626741164058</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="15">
         <v>2.10189275442536E-2</v>
       </c>
-      <c r="P16" s="35">
+      <c r="P16" s="25">
         <v>0.1</v>
       </c>
-      <c r="Q16" s="35">
-        <v>0</v>
-      </c>
-      <c r="R16" s="35">
+      <c r="Q16" s="25">
+        <v>0</v>
+      </c>
+      <c r="R16" s="25">
         <v>6.479643687803946E-2</v>
       </c>
-      <c r="S16" s="35">
+      <c r="S16" s="25">
         <v>0.12618253497302423</v>
       </c>
-      <c r="T16" s="35">
+      <c r="T16" s="25">
         <v>8.1848130793313004E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="U16" s="25">
+        <v>8.6137865248475831E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="20">
+      <c r="D17" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="16">
         <v>7.6543304374449847E-3</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="16">
         <v>3.7869607367910806E-2</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="16">
         <v>0.14977907586310193</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="16">
         <v>5.9173348323914909E-2</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="11">
         <v>4.382665098646487E-2</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="11">
         <v>0.12997891453164265</v>
       </c>
-      <c r="L17" s="15">
+      <c r="L17" s="11">
         <v>0.10709695844638013</v>
       </c>
-      <c r="M17" s="15">
+      <c r="M17" s="11">
         <v>0.11282463525910882</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="11">
         <v>0.1392961366216508</v>
       </c>
-      <c r="O17" s="15">
+      <c r="O17" s="11">
         <v>6.8841128443777452E-3</v>
       </c>
-      <c r="P17" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="36">
-        <v>0</v>
-      </c>
-      <c r="R17" s="36">
+      <c r="P17" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="26">
+        <v>0</v>
+      </c>
+      <c r="R17" s="26">
         <v>7.643825526207898E-2</v>
       </c>
-      <c r="S17" s="36">
+      <c r="S17" s="26">
         <v>0.15767275020694549</v>
       </c>
-      <c r="T17" s="36">
+      <c r="T17" s="26">
         <v>9.5644356026550872E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="U17" s="26">
+        <v>9.0562132091338371E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="24">
+      <c r="D18" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="19">
         <v>7.7015495517698167E-3</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="19">
         <v>7.6543304374449847E-3</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="19">
         <v>3.7869607367910806E-2</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="19">
         <v>0.14977907586310193</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="19">
         <v>5.9173348323914909E-2</v>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="19">
         <v>4.382665098646487E-2</v>
       </c>
-      <c r="K18" s="24">
+      <c r="K18" s="19">
         <v>0.12997891453164265</v>
       </c>
-      <c r="L18" s="24">
+      <c r="L18" s="19">
         <v>0.10709695844638013</v>
       </c>
-      <c r="M18" s="24">
+      <c r="M18" s="19">
         <v>0.11282463525910882</v>
       </c>
-      <c r="N18" s="24">
+      <c r="N18" s="19">
         <v>0.1392961366216508</v>
       </c>
-      <c r="O18" s="24">
+      <c r="O18" s="19">
         <v>6.8841128443777452E-3</v>
       </c>
-      <c r="P18" s="36">
+      <c r="P18" s="26">
         <v>0.1</v>
       </c>
-      <c r="Q18" s="36">
-        <v>0</v>
-      </c>
-      <c r="R18" s="36">
+      <c r="Q18" s="26">
+        <v>0</v>
+      </c>
+      <c r="R18" s="26">
         <v>5.3576570965516782E-2</v>
       </c>
-      <c r="S18" s="36">
+      <c r="S18" s="26">
         <v>8.3781780685077176E-2</v>
       </c>
-      <c r="T18" s="36">
+      <c r="T18" s="26">
         <v>5.8688124783995099E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="U18" s="26">
+        <v>8.1832545432799747E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="17">
         <v>9.5398283201381134E-2</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="17">
         <v>0.11895916223467531</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="17">
         <v>0.10997024493618571</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="17">
         <v>9.0725779552366118E-2</v>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="17">
         <v>8.7779434858442501E-2</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="17">
         <v>0.17151002945835581</v>
       </c>
-      <c r="J19" s="19">
+      <c r="J19" s="15">
         <v>6.1525598863209206E-2</v>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="15">
         <v>7.742717726869866E-2</v>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="15">
         <v>7.8784278195325519E-2</v>
       </c>
-      <c r="M19" s="19">
+      <c r="M19" s="15">
         <v>7.8524370038241365E-2</v>
       </c>
-      <c r="N19" s="19">
+      <c r="N19" s="15">
         <v>8.0727624993272698E-2</v>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="15">
         <v>6.8531630736511695E-2</v>
       </c>
-      <c r="P19" s="35">
+      <c r="P19" s="25">
         <v>0.1</v>
       </c>
-      <c r="Q19" s="35">
-        <v>0</v>
-      </c>
-      <c r="R19" s="35">
+      <c r="Q19" s="25">
+        <v>0</v>
+      </c>
+      <c r="R19" s="25">
         <v>5.4163459619715498E-2</v>
       </c>
-      <c r="S19" s="35">
+      <c r="S19" s="25">
         <v>8.9790167285988584E-2</v>
       </c>
-      <c r="T19" s="35">
+      <c r="T19" s="25">
         <v>9.1518908823439687E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="U19" s="25">
+        <v>7.4729319728326901E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="16">
         <v>6.9081919954592647E-2</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="16">
         <v>0.12175032697341599</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="16">
         <v>0.10722515829341166</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="16">
         <v>9.3199651576687179E-2</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="16">
         <v>9.0158254253348238E-2</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="16">
         <v>0.15104848482744013</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="11">
         <v>6.454812912343641E-2</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="11">
         <v>7.3071615165017298E-2</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="11">
         <v>7.783299957029699E-2</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="11">
         <v>8.558794161000427E-2</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20" s="11">
         <v>8.5416724905342745E-2</v>
       </c>
-      <c r="O20" s="15">
+      <c r="O20" s="11">
         <v>5.7836723884436135E-2</v>
       </c>
-      <c r="P20" s="36">
+      <c r="P20" s="26">
         <v>0.1</v>
       </c>
-      <c r="Q20" s="36">
-        <v>0</v>
-      </c>
-      <c r="R20" s="36">
+      <c r="Q20" s="26">
+        <v>0</v>
+      </c>
+      <c r="R20" s="26">
         <v>6.4872252119520635E-2</v>
       </c>
-      <c r="S20" s="36">
+      <c r="S20" s="26">
         <v>0.11543537913568107</v>
       </c>
-      <c r="T20" s="36">
+      <c r="T20" s="26">
         <v>0.11305183426601097</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="U20" s="26">
+        <v>0.1007029062858754</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="19">
         <v>0.1213039067209716</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="19">
         <v>0.11621171595677651</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="19">
         <v>0.11267162302578748</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="19">
         <v>8.8288526905928574E-2</v>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="19">
         <v>8.5433277482054648E-2</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="19">
         <v>0.19167973055306448</v>
       </c>
-      <c r="J21" s="24">
+      <c r="J21" s="19">
         <v>5.8548988775322441E-2</v>
       </c>
-      <c r="K21" s="24">
+      <c r="K21" s="19">
         <v>8.1713365855252948E-2</v>
       </c>
-      <c r="L21" s="24">
+      <c r="L21" s="19">
         <v>7.9719641963144017E-2</v>
       </c>
-      <c r="M21" s="24">
+      <c r="M21" s="19">
         <v>7.1588645418326685E-2</v>
       </c>
-      <c r="N21" s="24">
+      <c r="N21" s="19">
         <v>7.6130383940752291E-2</v>
       </c>
-      <c r="O21" s="24">
+      <c r="O21" s="19">
         <v>7.9006368211415073E-2</v>
       </c>
-      <c r="P21" s="36">
+      <c r="P21" s="26">
         <v>0.1</v>
       </c>
-      <c r="Q21" s="36">
-        <v>0</v>
-      </c>
-      <c r="R21" s="36">
+      <c r="Q21" s="26">
+        <v>0</v>
+      </c>
+      <c r="R21" s="26">
         <v>4.3693418784505472E-2</v>
       </c>
-      <c r="S21" s="36">
+      <c r="S21" s="26">
         <v>6.4489306438090949E-2</v>
       </c>
-      <c r="T21" s="36">
+      <c r="T21" s="26">
         <v>6.9664232061118755E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+      <c r="U21" s="26">
+        <v>4.9298760347457664E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="17">
         <v>1.3473759852686893E-2</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="17">
         <v>1.7774775815640024E-2</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="17">
         <v>3.0750037339331057E-2</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="17">
         <v>2.1701200510412237E-2</v>
       </c>
-      <c r="H22" s="21">
+      <c r="H22" s="17">
         <v>4.2815000663632509E-2</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="17">
         <v>6.7396798652064022E-2</v>
       </c>
-      <c r="J22" s="19">
+      <c r="J22" s="15">
         <v>4.5566578985522257E-2</v>
       </c>
-      <c r="K22" s="19">
+      <c r="K22" s="15">
         <v>4.8926870637354035E-2</v>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="15">
         <v>5.6170984476747218E-2</v>
       </c>
-      <c r="M22" s="19">
+      <c r="M22" s="15">
         <v>5.529204071073969E-2</v>
       </c>
-      <c r="N22" s="19">
+      <c r="N22" s="15">
         <v>5.8354405757634703E-2</v>
       </c>
-      <c r="O22" s="19">
+      <c r="O22" s="15">
         <v>5.7429237607727675E-2</v>
       </c>
-      <c r="P22" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="35">
-        <v>0</v>
-      </c>
-      <c r="R22" s="35">
+      <c r="P22" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="25">
+        <v>0</v>
+      </c>
+      <c r="R22" s="25">
         <v>5.1373884452794741E-2</v>
       </c>
-      <c r="S22" s="35">
+      <c r="S22" s="25">
         <v>7.7235413540471365E-2</v>
       </c>
-      <c r="T22" s="35">
+      <c r="T22" s="25">
         <v>7.2646437055494617E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="U22" s="25">
+        <v>6.8152877665584588E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="16">
         <v>8.9803689135549685E-3</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="16">
         <v>8.8923667923454502E-3</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="16">
         <v>1.7600520975420871E-2</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="16">
         <v>8.7049626992348333E-3</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="16">
         <v>1.7202821262687081E-2</v>
       </c>
-      <c r="I23" s="20">
+      <c r="I23" s="16">
         <v>6.7801781491808696E-2</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="11">
         <v>5.0049632552281009E-2</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="11">
         <v>4.1100507180258601E-2</v>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="11">
         <v>4.8590077906091579E-2</v>
       </c>
-      <c r="M23" s="15">
+      <c r="M23" s="11">
         <v>4.7870176082464355E-2</v>
       </c>
-      <c r="N23" s="15">
+      <c r="N23" s="11">
         <v>5.5043130224182807E-2</v>
       </c>
-      <c r="O23" s="15">
+      <c r="O23" s="11">
         <v>4.6446099301760302E-2</v>
       </c>
-      <c r="P23" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="36">
-        <v>0</v>
-      </c>
-      <c r="R23" s="36">
+      <c r="P23" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="26">
+        <v>0</v>
+      </c>
+      <c r="R23" s="26">
         <v>2.9662368095156877E-2</v>
       </c>
-      <c r="S23" s="36">
+      <c r="S23" s="26">
         <v>0.1335826876836762</v>
       </c>
-      <c r="T23" s="36">
+      <c r="T23" s="26">
         <v>7.1977140060316844E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="U23" s="26">
+        <v>5.8019363962722559E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="19">
         <v>1.7969290482565296E-2</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="19">
         <v>2.6647243786750992E-2</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="19">
         <v>4.3856186792270789E-2</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="19">
         <v>3.4624540142826232E-2</v>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="19">
         <v>6.8199449289446989E-2</v>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="19">
         <v>6.6996625045013358E-2</v>
       </c>
-      <c r="J24" s="24">
+      <c r="J24" s="19">
         <v>4.1144136137717655E-2</v>
       </c>
-      <c r="K24" s="24">
+      <c r="K24" s="19">
         <v>5.6629264385855624E-2</v>
       </c>
-      <c r="L24" s="24">
+      <c r="L24" s="19">
         <v>6.3614749079574109E-2</v>
       </c>
-      <c r="M24" s="24">
+      <c r="M24" s="19">
         <v>6.2567455538001901E-2</v>
       </c>
-      <c r="N24" s="24">
+      <c r="N24" s="19">
         <v>6.1596741532372941E-2</v>
       </c>
-      <c r="O24" s="24">
+      <c r="O24" s="19">
         <v>6.8177169738426927E-2</v>
       </c>
-      <c r="P24" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="36">
-        <v>0</v>
-      </c>
-      <c r="R24" s="36">
+      <c r="P24" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="26">
+        <v>0</v>
+      </c>
+      <c r="R24" s="26">
         <v>7.2642215296997686E-2</v>
       </c>
-      <c r="S24" s="36">
+      <c r="S24" s="26">
         <v>2.1874179718260566E-2</v>
       </c>
-      <c r="T24" s="36">
+      <c r="T24" s="26">
         <v>7.3328298123528854E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+      <c r="U24" s="26">
+        <v>7.8069552874379E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="17">
         <v>0.1200436200606789</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="17">
         <v>0.21175556641481538</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="17">
         <v>0.3169249086821268</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="17">
         <v>0.24650031182289447</v>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="17">
         <v>0.25167406010123161</v>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="17">
         <v>0.24570705215373073</v>
       </c>
-      <c r="J25" s="19">
+      <c r="J25" s="15">
         <v>0.18560640093819897</v>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="15">
         <v>0.22278175510251441</v>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="15">
         <v>0.18890856370315409</v>
       </c>
-      <c r="M25" s="19">
+      <c r="M25" s="15">
         <v>0.29350516591411796</v>
       </c>
-      <c r="N25" s="19">
+      <c r="N25" s="15">
         <v>0.30662249842582201</v>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="15">
         <v>0.23517763428481836</v>
       </c>
-      <c r="P25" s="35">
+      <c r="P25" s="25">
         <v>0.2</v>
       </c>
-      <c r="Q25" s="35">
+      <c r="Q25" s="25">
         <v>0.1</v>
       </c>
-      <c r="R25" s="35">
+      <c r="R25" s="25">
         <v>0.13772601093442507</v>
       </c>
-      <c r="S25" s="35">
+      <c r="S25" s="25">
         <v>0.13849188927432132</v>
       </c>
-      <c r="T25" s="35">
+      <c r="T25" s="25">
         <v>0.11692151225912777</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="U25" s="25">
+        <v>0.15452119688593122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="16">
         <v>4.4666674938273136E-2</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="16">
         <v>7.8746164200517263E-2</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="16">
         <v>8.3016324916129092E-2</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="16">
         <v>8.479729811580404E-2</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="16">
         <v>0.10574203269832039</v>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="16">
         <v>0.20866233218094818</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="11">
         <v>0.13969829824189692</v>
       </c>
-      <c r="K26" s="15">
+      <c r="K26" s="11">
         <v>0.15769446126772635</v>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="11">
         <v>0.1860807141912327</v>
       </c>
-      <c r="M26" s="15">
+      <c r="M26" s="11">
         <v>0.22426355805128162</v>
       </c>
-      <c r="N26" s="15">
+      <c r="N26" s="11">
         <v>0.22432551357600752</v>
       </c>
-      <c r="O26" s="15">
+      <c r="O26" s="11">
         <v>0.1776995523663657</v>
       </c>
-      <c r="P26" s="36">
+      <c r="P26" s="26">
         <v>0.2</v>
       </c>
-      <c r="Q26" s="36">
+      <c r="Q26" s="26">
         <v>0.2</v>
       </c>
-      <c r="R26" s="36">
+      <c r="R26" s="26">
         <v>0.15668565643254884</v>
       </c>
-      <c r="S26" s="36">
+      <c r="S26" s="26">
         <v>0.15541703258327452</v>
       </c>
-      <c r="T26" s="36">
+      <c r="T26" s="26">
         <v>9.2204309998266565E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="U26" s="26">
+        <v>0.15751556502491232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="19">
         <v>0.19825229020015758</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="19">
         <v>0.34973871709711757</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="19">
         <v>0.55942427395082628</v>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="19">
         <v>0.41393947452265251</v>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="19">
         <v>0.40257248789797517</v>
       </c>
-      <c r="I27" s="24">
+      <c r="I27" s="19">
         <v>0.28394974089586145</v>
       </c>
-      <c r="J27" s="24">
+      <c r="J27" s="19">
         <v>0.23296083616128574</v>
       </c>
-      <c r="K27" s="24">
+      <c r="K27" s="19">
         <v>0.28990631076542334</v>
       </c>
-      <c r="L27" s="24">
+      <c r="L27" s="19">
         <v>0.19182368860775292</v>
       </c>
-      <c r="M27" s="24">
+      <c r="M27" s="19">
         <v>0.36487748275330656</v>
       </c>
-      <c r="N27" s="24">
+      <c r="N27" s="19">
         <v>0.39149129265531191</v>
       </c>
-      <c r="O27" s="24">
+      <c r="O27" s="19">
         <v>0.29443645952152986</v>
       </c>
-      <c r="P27" s="36">
+      <c r="P27" s="26">
         <v>0.3</v>
       </c>
-      <c r="Q27" s="36">
+      <c r="Q27" s="26">
         <v>0.1</v>
       </c>
-      <c r="R27" s="36">
+      <c r="R27" s="26">
         <v>0.11816042869432726</v>
       </c>
-      <c r="S27" s="36">
+      <c r="S27" s="26">
         <v>0.12135301021830269</v>
       </c>
-      <c r="T27" s="36">
+      <c r="T27" s="26">
         <v>0.14195736796096919</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+      <c r="U27" s="26">
+        <v>0.1515223848377984</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="17">
         <v>5.5034629011565833E-2</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="17">
         <v>8.0991627641596328E-2</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="17">
         <v>9.1729785495257454E-2</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="17">
         <v>0.10667729532026633</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="17">
         <v>0.12341848439794272</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I28" s="17">
         <v>8.8197580672517858E-2</v>
       </c>
-      <c r="J28" s="19">
+      <c r="J28" s="15">
         <v>0.10607547269882521</v>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="15">
         <v>9.7147952013229399E-2</v>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="15">
         <v>0.12238959350828715</v>
       </c>
-      <c r="M28" s="19">
+      <c r="M28" s="15">
         <v>0.1330876542114505</v>
       </c>
-      <c r="N28" s="19">
+      <c r="N28" s="15">
         <v>0.13015473278930673</v>
       </c>
-      <c r="O28" s="19">
+      <c r="O28" s="15">
         <v>0.31250677755235229</v>
       </c>
-      <c r="P28" s="35">
+      <c r="P28" s="25">
         <v>0.3</v>
       </c>
-      <c r="Q28" s="35">
+      <c r="Q28" s="25">
         <v>0.3</v>
       </c>
-      <c r="R28" s="35">
+      <c r="R28" s="25">
         <v>0.33417383115107696</v>
       </c>
-      <c r="S28" s="35">
+      <c r="S28" s="25">
         <v>0.4304881257025327</v>
       </c>
-      <c r="T28" s="35">
+      <c r="T28" s="25">
         <v>0.39313622256705832</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="U28" s="25">
+        <v>0.3761930941040908</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="16">
         <v>2.9707563317100817E-2</v>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="16">
         <v>5.4107796257093194E-2</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29" s="16">
         <v>3.7757640369580667E-2</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="16">
         <v>4.5934571671055968E-2</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="16">
         <v>5.1685373900609025E-2</v>
       </c>
-      <c r="I29" s="20">
+      <c r="I29" s="16">
         <v>4.0146895377190649E-2</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="11">
         <v>4.960327712317527E-2</v>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="11">
         <v>8.691679838941152E-2</v>
       </c>
-      <c r="L29" s="15">
+      <c r="L29" s="11">
         <v>8.5076242162598514E-2</v>
       </c>
-      <c r="M29" s="15">
+      <c r="M29" s="11">
         <v>9.6836918881649789E-2</v>
       </c>
-      <c r="N29" s="15">
+      <c r="N29" s="11">
         <v>8.1493723088119363E-2</v>
       </c>
-      <c r="O29" s="15">
+      <c r="O29" s="11">
         <v>0.1927471472495538</v>
       </c>
-      <c r="P29" s="36">
+      <c r="P29" s="26">
         <v>0.3</v>
       </c>
-      <c r="Q29" s="36">
+      <c r="Q29" s="26">
         <v>0.4</v>
       </c>
-      <c r="R29" s="36">
+      <c r="R29" s="26">
         <v>0.41139191068108794</v>
       </c>
-      <c r="S29" s="36">
+      <c r="S29" s="26">
         <v>0.49554896622979544</v>
       </c>
-      <c r="T29" s="36">
+      <c r="T29" s="26">
         <v>0.26099583355742068</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="U29" s="26">
+        <v>0.45818790187772973</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="19">
         <v>8.4195459759832447E-2</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="19">
         <v>0.11207051581106475</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="19">
         <v>0.15416951452019878</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="19">
         <v>0.17682661897400143</v>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="19">
         <v>0.20614920731904199</v>
       </c>
-      <c r="I30" s="24">
+      <c r="I30" s="19">
         <v>0.1435118068866208</v>
       </c>
-      <c r="J30" s="24">
+      <c r="J30" s="19">
         <v>0.17094950578972737</v>
       </c>
-      <c r="K30" s="24">
+      <c r="K30" s="19">
         <v>0.10887291056669508</v>
       </c>
-      <c r="L30" s="24">
+      <c r="L30" s="19">
         <v>0.16502247018292629</v>
       </c>
-      <c r="M30" s="24">
+      <c r="M30" s="19">
         <v>0.17441064655572089</v>
       </c>
-      <c r="N30" s="24">
+      <c r="N30" s="19">
         <v>0.1855527746612583</v>
       </c>
-      <c r="O30" s="24">
+      <c r="O30" s="19">
         <v>0.44859954803069008</v>
       </c>
-      <c r="P30" s="36">
+      <c r="P30" s="26">
         <v>0.5</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="Q30" s="26">
         <v>0.2</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="26">
         <v>0.24697746624641295</v>
       </c>
-      <c r="S30" s="36">
+      <c r="S30" s="26">
         <v>0.35193780867878632</v>
       </c>
-      <c r="T30" s="36">
+      <c r="T30" s="26">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+      <c r="U30" s="26">
+        <v>0.27770391040766934</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="17">
         <v>0.34344009897319216</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="17">
         <v>0.24472196865228116</v>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="17">
         <v>0.49529853345199865</v>
       </c>
-      <c r="G31" s="21">
+      <c r="G31" s="17">
         <v>0.29525914817735749</v>
       </c>
-      <c r="H31" s="21">
+      <c r="H31" s="17">
         <v>0.23457016971151778</v>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="17">
         <v>0.25573069233272888</v>
       </c>
-      <c r="J31" s="19">
+      <c r="J31" s="15">
         <v>0.1902754046206479</v>
       </c>
-      <c r="K31" s="19">
+      <c r="K31" s="15">
         <v>0.21293207466818087</v>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="15">
         <v>0.15019360321780637</v>
       </c>
-      <c r="M31" s="19">
+      <c r="M31" s="15">
         <v>0.19010929490973397</v>
       </c>
-      <c r="N31" s="19">
+      <c r="N31" s="15">
         <v>0.15070322329661548</v>
       </c>
-      <c r="O31" s="19">
+      <c r="O31" s="15">
         <v>0.16661679497293325</v>
       </c>
-      <c r="P31" s="38">
+      <c r="P31" s="25">
         <v>0.2</v>
       </c>
-      <c r="Q31" s="38">
+      <c r="Q31" s="25">
         <v>0.2</v>
       </c>
-      <c r="R31" s="38">
+      <c r="R31" s="25">
         <v>0.16773611144997194</v>
       </c>
-      <c r="S31" s="38">
+      <c r="S31" s="25">
         <v>0.21076296192215821</v>
       </c>
-      <c r="T31" s="38">
+      <c r="T31" s="25">
         <v>0.19508978251610865</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="U31" s="25">
+        <v>0.13666774150150868</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="16">
         <v>0.12749362531873407</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="16">
         <v>0.11941189641017987</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="16">
         <v>0.26052909737833291</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="16">
         <v>0.17924359204158449</v>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="16">
         <v>0.16510442855105856</v>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="16">
         <v>0.20841552100158545</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="11">
         <v>0.19044689095450518</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="11">
         <v>0.23048942989880072</v>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="11">
         <v>0.12024331588626397</v>
       </c>
-      <c r="M32" s="15">
+      <c r="M32" s="11">
         <v>0.18721268053889517</v>
       </c>
-      <c r="N32" s="15">
+      <c r="N32" s="11">
         <v>0.14240956992309883</v>
       </c>
-      <c r="O32" s="15">
+      <c r="O32" s="11">
         <v>0.15157506260709108</v>
       </c>
-      <c r="P32" s="36">
+      <c r="P32" s="26">
         <v>0.1</v>
       </c>
-      <c r="Q32" s="36">
+      <c r="Q32" s="26">
         <v>0.2</v>
       </c>
-      <c r="R32" s="36">
+      <c r="R32" s="26">
         <v>0.1959922553363346</v>
       </c>
-      <c r="S32" s="36">
+      <c r="S32" s="26">
         <v>0.25905990040586052</v>
       </c>
-      <c r="T32" s="36">
+      <c r="T32" s="26">
         <v>0.1687649778917879</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="U32" s="26">
+        <v>0.16863770998637925</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="19">
         <v>0.57774776021026764</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="19">
         <v>0.38073636032241082</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="19">
         <v>0.74946811939913605</v>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="19">
         <v>0.4210355856038217</v>
       </c>
-      <c r="H33" s="24">
+      <c r="H33" s="19">
         <v>0.31010788490101027</v>
       </c>
-      <c r="I33" s="24">
+      <c r="I33" s="19">
         <v>0.30710296839263923</v>
       </c>
-      <c r="J33" s="24">
+      <c r="J33" s="19">
         <v>0.19008997592193638</v>
       </c>
-      <c r="K33" s="24">
+      <c r="K33" s="19">
         <v>0.19401502452349911</v>
       </c>
-      <c r="L33" s="24">
+      <c r="L33" s="19">
         <v>0.18236943488271365</v>
       </c>
-      <c r="M33" s="24">
+      <c r="M33" s="19">
         <v>0.19321373898310124</v>
       </c>
-      <c r="N33" s="24">
+      <c r="N33" s="19">
         <v>0.15957408226769276</v>
       </c>
-      <c r="O33" s="24">
+      <c r="O33" s="19">
         <v>0.18265096805013067</v>
       </c>
-      <c r="P33" s="37">
+      <c r="P33" s="26">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="37">
+      <c r="Q33" s="26">
         <v>0.1</v>
       </c>
-      <c r="R33" s="37">
+      <c r="R33" s="26">
         <v>0.13791201213625709</v>
       </c>
-      <c r="S33" s="37">
+      <c r="S33" s="26">
         <v>0.1647039446594746</v>
       </c>
-      <c r="T33" s="37">
+      <c r="T33" s="26">
         <v>0.22022527434160699</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="29" t="s">
+      <c r="U33" s="26">
+        <v>0.10547455110031051</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="37"/>
-      <c r="Q34" s="37"/>
-      <c r="R34" s="37"/>
-      <c r="S34" s="37"/>
-      <c r="T34" s="37"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="26"/>
+      <c r="S34" s="26"/>
+      <c r="T34" s="26"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="16">
         <v>2.8574783002476688E-2</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="16">
         <v>6.0680851538104791E-2</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="16">
         <v>3.0757438840370736E-2</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="16">
         <v>2.6760539395163152E-2</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H35" s="16">
         <v>3.4624095743982272E-2</v>
       </c>
-      <c r="I35" s="20">
+      <c r="I35" s="16">
         <v>9.137341813407332E-2</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="11">
         <v>1.3579937453071414E-2</v>
       </c>
-      <c r="K35" s="15">
+      <c r="K35" s="11">
         <v>1.97835242809788E-2</v>
       </c>
-      <c r="L35" s="15">
+      <c r="L35" s="11">
         <v>1.6499287603340095E-2</v>
       </c>
-      <c r="M35" s="15">
+      <c r="M35" s="11">
         <v>1.6499888883560802E-2</v>
       </c>
-      <c r="N35" s="15">
+      <c r="N35" s="11">
         <v>1.5035438528611939E-2</v>
       </c>
-      <c r="O35" s="15">
+      <c r="O35" s="11">
         <v>1.6559161989515129E-2</v>
       </c>
-      <c r="P35" s="39">
+      <c r="P35" s="26">
         <v>1.3237005751478998E-2</v>
       </c>
-      <c r="Q35" s="39">
-        <v>0</v>
-      </c>
-      <c r="R35" s="39">
-        <v>0</v>
-      </c>
-      <c r="S35" s="39">
-        <v>0</v>
-      </c>
-      <c r="T35" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="Q35" s="26">
+        <v>0</v>
+      </c>
+      <c r="R35" s="26">
+        <v>0</v>
+      </c>
+      <c r="S35" s="26">
+        <v>0</v>
+      </c>
+      <c r="T35" s="26">
+        <v>0</v>
+      </c>
+      <c r="U35" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="19">
         <v>0.11669018515243708</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="19">
         <v>0.14821202403729553</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="19">
         <v>0.2145853381744201</v>
       </c>
-      <c r="G36" s="24">
+      <c r="G36" s="19">
         <v>0.17419765933355644</v>
       </c>
-      <c r="H36" s="24">
+      <c r="H36" s="19">
         <v>0.17729566019206405</v>
       </c>
-      <c r="I36" s="24">
+      <c r="I36" s="19">
         <v>0.17800449287726169</v>
       </c>
-      <c r="J36" s="24">
+      <c r="J36" s="19">
         <v>0.14731037870836131</v>
       </c>
-      <c r="K36" s="24">
+      <c r="K36" s="19">
         <v>0.17310058316276145</v>
       </c>
-      <c r="L36" s="24">
+      <c r="L36" s="19">
         <v>0.16555403630124133</v>
       </c>
-      <c r="M36" s="24">
+      <c r="M36" s="19">
         <v>0.19981732849773223</v>
       </c>
-      <c r="N36" s="24">
+      <c r="N36" s="19">
         <v>0.22063464046394862</v>
       </c>
-      <c r="O36" s="24">
+      <c r="O36" s="19">
         <v>0.21601828170764617</v>
       </c>
-      <c r="P36" s="39">
+      <c r="P36" s="26">
         <v>6.7974429961575017E-2</v>
       </c>
-      <c r="Q36" s="39">
+      <c r="Q36" s="26">
         <v>0.1</v>
       </c>
-      <c r="R36" s="39">
+      <c r="R36" s="26">
         <v>0.1</v>
       </c>
-      <c r="S36" s="39">
+      <c r="S36" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="T36" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="U36" s="28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="H37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="I37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="J37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="K37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="M37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="N37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="O37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="P37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="R37" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="S37" s="26">
         <v>0.1</v>
       </c>
-      <c r="T36" s="39">
+      <c r="T37" s="26">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="31" t="s">
+      <c r="U37" s="26">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="31" t="s">
+      <c r="B38" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C38" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="32">
+      <c r="D38" s="16">
         <v>0.11669018515243708</v>
       </c>
-      <c r="E37" s="32">
+      <c r="E38" s="16">
         <v>0.14821202403729553</v>
       </c>
-      <c r="F37" s="32">
+      <c r="F38" s="16">
         <v>0.2145853381744201</v>
       </c>
-      <c r="G37" s="32">
+      <c r="G38" s="16">
         <v>0.17419765933355644</v>
       </c>
-      <c r="H37" s="32">
+      <c r="H38" s="16">
         <v>0.17729566019206405</v>
       </c>
-      <c r="I37" s="32">
+      <c r="I38" s="16">
         <v>0.17800449287726169</v>
       </c>
-      <c r="J37" s="33">
+      <c r="J38" s="11">
         <v>0.14731037870836131</v>
       </c>
-      <c r="K37" s="33">
+      <c r="K38" s="11">
         <v>0.17310058316276145</v>
       </c>
-      <c r="L37" s="33">
+      <c r="L38" s="11">
         <v>0.16555403630124133</v>
       </c>
-      <c r="M37" s="33">
+      <c r="M38" s="11">
         <v>0.19981732849773223</v>
       </c>
-      <c r="N37" s="33">
+      <c r="N38" s="11">
         <v>0.22063464046394862</v>
       </c>
-      <c r="O37" s="33">
+      <c r="O38" s="11">
         <v>0.21601828170764617</v>
       </c>
-      <c r="P37" s="40">
+      <c r="P38" s="11">
         <v>0.13623740240686077</v>
       </c>
-      <c r="Q37" s="40">
+      <c r="Q38" s="11">
         <v>0.2</v>
       </c>
-      <c r="R37" s="40">
+      <c r="R38" s="11">
         <v>0.2</v>
       </c>
-      <c r="S37" s="40">
+      <c r="S38" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="T38" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="U38" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="H39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="I39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="K39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="N39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="O39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="P39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="R39" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="S39" s="24">
         <v>0.2</v>
       </c>
-      <c r="T37" s="40">
+      <c r="T39" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="U39" s="24">
         <v>0.2</v>
       </c>
     </row>
